--- a/bd.xlsx
+++ b/bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\sup\python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\apps\sup\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C738DE-196F-4190-8C71-59DC99A3AEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCF693D-B3B7-4074-B8FC-CE06B8DBE0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{4EC11E8E-C16C-445D-8165-DA989CE60B99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4EC11E8E-C16C-445D-8165-DA989CE60B99}"/>
   </bookViews>
   <sheets>
     <sheet name="SHOWROOM" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>Producto</t>
   </si>
@@ -56,107 +56,16 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>.- Reducción de triglicéridos: Ayuda a disminuir la producción de grasas en el hígado, reduciendo de manera notable los niveles de triglicéridos en la sangre
-.- Acción antiinflamatoria: Bloquea los procesos celulares que generan inflamación crónica. Es ideal para aliviar molestias articulares, rigidez y para mejorar la recuperación muscular tras el ejercicio físico
-.- Protección arterial: Promueve la elasticidad de las arterias, reduce de forma discreta la presión arterial y evita la agregación de plaquetas, disminuyendo el riesgo de coágulos (efecto antitrombótico)
-.- Función cognitiva: Favorece la memoria, la concentración, la claridad mental y la correcta comunicación entre neuronas
-.- Salud visual: Es un elemento fundamental de la retina. Protege las células del ojo y contribuye a mantener una vista saludable a lo largo del tiempo</t>
-  </si>
-  <si>
-    <t>.- Mejora la digestión: El vinagre ayuda a equilibrar los niveles de ácido en el estómago, lo que facilita la descomposición de los alimentos y puede reducir la sensación de pesadez o indigestión después de comer
-.- Efecto bionutritivo: Contienen bacterias amigables y enzimas que apoyan la salud de la microbiota intestinal
-.- Regulación de la glucosa: El ácido acético ayuda a mejorar la sensibilidad a la insulina. Esto significa que puede suavizar los "picos de azúcar" en la sangre que ocurren después de consumir carbohidratos
-.- Efecto saciante: Al mantener el azúcar en sangre más estable, ayuda a reducir los antojos repentinos de dulce y promueve una mayor sensación de saciedad durante el día</t>
-  </si>
-  <si>
-    <t>.- Piel y elasticidad: Ayuda a mantener la piel firme y favorece una cicatrización más rápida de heridas o quemaduras
-.- Articulaciones y vasos sanguíneos: Refuerza las paredes de las arterias y da estructura a los cartílagos y tendones
-.- Estimula la producción y el correcto funcionamiento de los glóbulos blancos (linfocitos y fagocitos), que son las células de defensa de tu cuerpo
-.- Ayuda a que las barreras epiteliales (como la mucosa de la nariz y los pulmones) se mantengan fuertes contra los patógenos
-.- Reducir la duración y la intensidad de los síntomas del virus común</t>
-  </si>
-  <si>
     <t>Imagen</t>
   </si>
   <si>
-    <t>imagenes/omega3.jpg</t>
-  </si>
-  <si>
-    <t>imagenes/vinagre.jpg</t>
-  </si>
-  <si>
-    <t>imagenes/magnesio.jpg</t>
-  </si>
-  <si>
-    <t>imagenes/vitaminac.jpg</t>
-  </si>
-  <si>
-    <t>Omega 3, 500 mg de Omega 3 por porción, 300 mg de EPA y 200 mg de DHA</t>
-  </si>
-  <si>
-    <t>NatureWise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gomitas orgánicas de vinagre de sidra de manzana | Suplemento vegano, sin gluten y sin OMG | USDA Orgánico </t>
-  </si>
-  <si>
     <t>60 días</t>
   </si>
   <si>
-    <t>100 días</t>
-  </si>
-  <si>
-    <t>imagenes/probiotico.jpg</t>
-  </si>
-  <si>
-    <t>imagenes/melatonina.jpg</t>
-  </si>
-  <si>
-    <t>Vitamina C + Escaramujos, Apoyo Inmunológico, 1000mg de Vitamina C, Cápsulas Recubiertas, Cápsulas Vegetarianas</t>
-  </si>
-  <si>
-    <t>Nature’s Bounty</t>
-  </si>
-  <si>
     <t>Duración</t>
   </si>
   <si>
-    <t>60 Cápsulas Blandas</t>
-  </si>
-  <si>
     <t>120 Gomitas</t>
-  </si>
-  <si>
-    <t>100 Cápsulas Recubiertas</t>
-  </si>
-  <si>
-    <t>90 Gomitas</t>
-  </si>
-  <si>
-    <t>60 Gomitas</t>
-  </si>
-  <si>
-    <t>Suplemento de complejo de magnesio – Magnesio 500 mg por porción – Mezcla 4 en 1 de alta absorción – Glicinato de magnesio 100% quelado con malato, citrato y óxido – Complejo vegano – Embotellado en Estados Unidos</t>
-  </si>
-  <si>
-    <t>Gomitas probióticas | 1 mil millones de UFC | Sabor frambuesa y limón | Suplemento sin OMG y sin gluten</t>
-  </si>
-  <si>
-    <t>Gomitas de melatonina de 5 mg | Sabor mixto de bayas | Suplemento vegano, sin OMG y sin gluten</t>
-  </si>
-  <si>
-    <t>Nature's Nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 Cápsulas </t>
-  </si>
-  <si>
-    <t>90 días</t>
-  </si>
-  <si>
-    <t>.- Soporte Digestivo: Ayuda a mantener, restaurar y equilibrar la flora bacteriana del sistema gastrointestinal, promoviendo una digestión mucho más ligera y eficiente
-.- Bienestar Inmunológico: Dado que una gran parte del sistema inmunitario reside en el intestino, el equilibrio de la microbiota favorece las defensas naturales del cuerpo
-.- Alivio de Molestias Comunes: Contribuye a disminuir problemas cotidianos como la hinchazón abdominal, los gases o la pesadez estomacal</t>
   </si>
   <si>
     <t>.- Conciliación del Sueño: Ayuda a reducir el tiempo necesario para quedarse dormido, actuando en armonía con el ciclo natural del cuerpo
@@ -164,21 +73,87 @@
 .- Regulación del Jet Lag o Turnos Laborales: Ayuda a sincronizar el reloj biológico cuando se sufren desajustes horarios debidos a viajes o trabajos nocturnos</t>
   </si>
   <si>
-    <t>.- Relajación y Alivio Muscular: Ayuda a reducir la tensión, los dolores musculares y los calambres nocturnos, promoviendo la recuperación post-entrenamiento
-.- Soporte al Sistema Nervioso y Descanso: El glicinato actúa directamente favoreciendo un estado de calma, ayudando a manejar el estrés diario y mejorando la calidad del sueño
-.- Salud Ósea y Cardiovascular: El magnesio es clave para la fijación del calcio en los huesos y contribuye a mantener un ritmo cardíaco saludable y una presión arterial estable
-.- Producción de Energía: El malato de magnesio interviene en el ciclo celular para ayudar al cuerpo a transformar los alimentos en energía disponible</t>
-  </si>
-  <si>
     <t>Presentación</t>
+  </si>
+  <si>
+    <t>melatonine.jpg</t>
+  </si>
+  <si>
+    <t>Vitafusion</t>
+  </si>
+  <si>
+    <t>100 Gomitas</t>
+  </si>
+  <si>
+    <t>33 días</t>
+  </si>
+  <si>
+    <t>multivitamin.jpg</t>
+  </si>
+  <si>
+    <t>Gomitas de melatonina de 5 mg, sabor a frambuesa</t>
+  </si>
+  <si>
+    <t>Gomitas multivitamínicas para el cabello, uñas de piel, además de biotina y vitaminas antioxidantes CE, sabor a frambuesa</t>
+  </si>
+  <si>
+    <t>.- Cabello más denso y fuerte: La alta concentración de biotina estimula los folículos pilosos, ayudando a reducir la caída y promoviendo un crecimiento acelerado
+.- Piel radiante y elástica: La vitamina C es un componente crucial para la producción natural de colágeno, lo que ayuda a mantener la firmeza de la piel y prevenir la aparición de arrugas prematuras
+.- Uñas resistentes: Fortalece la estructura de la queratina, previniendo el quiebre, las estrías y la descamación de las uñas</t>
+  </si>
+  <si>
+    <t>vinagre.jpg</t>
+  </si>
+  <si>
+    <t>.- Salud digestiva y metabólica: Apoya la digestión saludable y el metabolismo energético gracias a los compuestos activos del vinagre de manzana
+.- Alternativa segura y amigable: Ofrece los beneficios del vinagre líquido tradicional sin provocar ardor estomacal ni dañar el esmalte dental con su alta acidez
+.- Apoyo al bienestar general: Utilizado frecuentemente para ayudar a mantener niveles estables de energía y como complemento para promover la sensación de saciedad</t>
+  </si>
+  <si>
+    <t>RenewLife</t>
+  </si>
+  <si>
+    <t>48 Gomitas</t>
+  </si>
+  <si>
+    <t>24 días</t>
+  </si>
+  <si>
+    <t>probiotic-women.png</t>
+  </si>
+  <si>
+    <t>.- Salud vaginal y urinaria: Contiene cepas como Lactobacillus rhamnosus GG y extracto de arándano (cranberry) para mantener el pH vaginal, el equilibrio de levaduras y la salud del tracto urinario
+.- Apoyo digestivo e inmunitario: Aporta miles de millones de UFC (unidades formadoras de colonias) y prebióticos de origen vegetal que nutren las bacterias buenas del intestino</t>
+  </si>
+  <si>
+    <t>Gomitas de probióticos para mujeres, salud vaginal, urinaria, digestiva e inmune</t>
+  </si>
+  <si>
+    <t>Gomitas orgánicas de vinagre de sidra de manzana, sabor mixto a cereza</t>
+  </si>
+  <si>
+    <t>30 días</t>
+  </si>
+  <si>
+    <t>multivitamin-men.png</t>
+  </si>
+  <si>
+    <t>Rainbow Light</t>
+  </si>
+  <si>
+    <t>.- Energía y Vitalidad Masculina: Contienen un complejo de vitaminas B formulado para apoyar la producción natural de energía celular y el metabolismo, ayudando a combatir la fatiga diaria
+.- Defensa Inmunológica: Su aporte de vitaminas antioxidantes (como la vitamina C) y vitamina D trabaja en conjunto para fortalecer el sistema inmunológico
+.- Salud Digestiva: A diferencia de muchas gomitas tradicionales, esta fórmula incluye probióticos y enzimas que promueven una flora intestinal saludable y facilitan la absorción de los nutrientes</t>
+  </si>
+  <si>
+    <t>Gomitas multivitamínicas con probióticos para hombres, sabor a arándanos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="7" formatCode="&quot;Bs.S&quot;#,##0.00;&quot;Bs.S&quot;\-#,##0.00"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-540A]#,##0.00_ ;\-[$$-540A]#,##0.00\ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -253,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -264,9 +239,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -286,7 +258,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -623,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797258AE-E458-41B9-9D2D-4E237428F030}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.77734375" style="1" customWidth="1"/>
@@ -638,213 +610,188 @@
     <col min="10" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="7">
+        <v>30</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="D3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="7">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="D4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7">
+        <v>30</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7">
+        <v>30</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="8">
-        <v>21</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="E6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="8">
-        <v>33</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="8">
-        <v>20</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="8">
-        <v>15</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8">
-        <v>21</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="8">
-        <v>19</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/bd.xlsx
+++ b/bd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\apps\sup\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCF693D-B3B7-4074-B8FC-CE06B8DBE0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A488FDF1-F186-4999-8F03-AB1A29CE9FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4EC11E8E-C16C-445D-8165-DA989CE60B99}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Producto</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Gomitas multivitamínicas con probióticos para hombres, sabor a arándanos</t>
+  </si>
+  <si>
+    <t>Stock</t>
   </si>
 </sst>
 </file>
@@ -228,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -259,6 +262,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -595,22 +601,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797258AE-E458-41B9-9D2D-4E237428F030}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="11.5546875" style="1"/>
+    <col min="5" max="6" width="13.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -627,13 +633,16 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
@@ -649,15 +658,18 @@
       <c r="E2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7">
         <v>30</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -673,15 +685,18 @@
       <c r="E3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="11">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7">
         <v>30</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
@@ -697,15 +712,18 @@
       <c r="E4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="11">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
@@ -721,15 +739,18 @@
       <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
         <v>30</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
@@ -745,53 +766,57 @@
       <c r="E6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
         <v>30</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" s="4"/>
+      <c r="H7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F16" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
